--- a/Outputs/PtX_demand_MT.xlsx
+++ b/Outputs/PtX_demand_MT.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,32 +488,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0.0003362737310847895</v>
+      </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>1.827624446796205e-05</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>4.101128240432117e-10</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5.162994137005741e-06</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -522,17 +518,23 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>1.827624446796205e-05</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>4.101128240432117e-10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.162994137005741e-06</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -551,7 +553,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -570,7 +572,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -579,21 +581,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>6.452553999631451e-06</v>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>8.397989397361688e-07</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -603,12 +601,12 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>7.03991754360106e-05</v>
+        <v>6.452553999631451e-06</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>3.691412585452613e-06</v>
+        <v>8.397989397361688e-07</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -616,7 +614,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -625,17 +623,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>7.03991754360106e-05</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>3.691412585452613e-06</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -644,25 +646,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.000346064562203222</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>0.0011221082647848</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0001757780853667028</v>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>0.0005524486940619629</v>
-      </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -672,24 +666,24 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.003325367738937833</v>
+        <v>0.000346064562203222</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0.0102554645064325</v>
+        <v>0.0011221082647848</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0011018500620336</v>
+        <v>0.0001757780853667028</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>0.005409986315309055</v>
+        <v>0.0005524486940619629</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -698,17 +692,25 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.003325367738937833</v>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0.0102554645064325</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0011018500620336</v>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0.005409986315309055</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -727,7 +729,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -736,76 +738,74 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="n">
-        <v>0.003766560275044659</v>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
-        <v>0.01137757318133012</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.001287322353062497</v>
-      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>0.005962435009371018</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>8.727433796592085e-05</v>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>3.433097310043139e-08</v>
-      </c>
-      <c r="I14" t="n">
-        <v>7.358350436273957e-06</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>0.0003362737310847895</v>
+      </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0.003766560275044659</v>
+      </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0.01137757318133012</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.001287322353062497</v>
+      </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>0.005962435009371018</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0.0004347633703284716</v>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -817,7 +817,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -827,12 +827,14 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3.285836061700991e-11</v>
+        <v>8.727433796592085e-05</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>3.433097310043139e-08</v>
+      </c>
       <c r="I17" t="n">
-        <v>2.22295410110442e-12</v>
+        <v>7.358350436273957e-06</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -840,7 +842,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -849,21 +851,17 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="n">
-        <v>7.710515658804638e-06</v>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>1.528587009732526e-06</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -872,21 +870,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>3.887300101110755e-05</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>3.895215178152039e-06</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -895,17 +889,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>3.285836061700991e-11</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>2.22295410110442e-12</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -915,24 +913,20 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>0.0001594408980537171</v>
+        <v>7.710515658804638e-06</v>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="n">
-        <v>0.0013660064530657</v>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.0001150800479230624</v>
+        <v>1.528587009732526e-06</v>
       </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>0.000625142156911351</v>
-      </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -942,24 +936,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.0009603169320751703</v>
+        <v>3.887300101110755e-05</v>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="n">
-        <v>0.0096689867292966</v>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.000487755378613</v>
+        <v>3.895215178152039e-06</v>
       </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>0.005248161989956104</v>
-      </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -978,7 +968,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -987,17 +977,25 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.0001594408980537171</v>
+      </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>0.0013660064530657</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0001150800479230624</v>
+      </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>0.000625142156911351</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1007,53 +1005,47 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.001253615717623081</v>
+        <v>0.0009603169320751703</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.0110350275133354</v>
+        <v>0.0096689867292966</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0006156175813831751</v>
+        <v>0.000487755378613</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>0.005873304146867454</v>
+        <v>0.005248161989956104</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.0001213175349813206</v>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>5.818823410047024e-08</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.169551836969147e-05</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1068,11 +1060,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -1087,53 +1079,57 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>0.0004347633703284716</v>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>3.847815179239901e-10</v>
+        <v>0.001253615717623081</v>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0.0110350275133354</v>
+      </c>
       <c r="I29" t="n">
-        <v>5.086557031515447e-11</v>
+        <v>0.0006156175813831751</v>
       </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>0.005873304146867454</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>0.000486317278643494</v>
+      </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="n">
-        <v>1.424394012031528e-06</v>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>4.451596508182899e-07</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1143,12 +1139,14 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>2.84332898097902e-06</v>
+        <v>0.0001213175349813206</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>5.818823410047024e-08</v>
+      </c>
       <c r="I31" t="n">
-        <v>1.485254891157024e-06</v>
+        <v>1.169551836969147e-05</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1156,7 +1154,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1165,25 +1163,17 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>1.357403602652891e-12</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="n">
-        <v>5.262851685878789e-11</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.95160571120915e-12</v>
-      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
-        <v>4.283859938684607e-11</v>
-      </c>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1192,25 +1182,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>2.131509547760184e-05</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="n">
-        <v>0.0017891741436655</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2.958439156361175e-05</v>
-      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>0.0008905614270451276</v>
-      </c>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1220,24 +1202,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>8.481940484330691e-05</v>
+        <v>3.847815179239901e-10</v>
       </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="n">
-        <v>0.0087685262034002</v>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>8.750451470732252e-05</v>
+        <v>5.086557031515447e-11</v>
       </c>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>0.004892386530442252</v>
-      </c>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1246,17 +1224,21 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>1.424394012031528e-06</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>4.451596508182899e-07</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1265,17 +1247,21 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>2.84332898097902e-06</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>1.485254891157024e-06</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1285,17 +1271,157 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>0.0002317201444341614</v>
+        <v>1.357403602652891e-12</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>0.01055775858792832</v>
+        <v>5.262851685878789e-11</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0001307148919997771</v>
+        <v>1.95160571120915e-12</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
+        <v>4.283859938684607e-11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>2.131509547760184e-05</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>0.0017891741436655</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.958439156361175e-05</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>0.0008905614270451276</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>8.481940484330691e-05</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>0.0087685262034002</v>
+      </c>
+      <c r="I39" t="n">
+        <v>8.750451470732252e-05</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>0.004892386530442252</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>0.000486317278643494</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>0.0002317201444341614</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>0.01055775858792832</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.0001307148919997771</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
         <v>0.005782948000325978</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_MT.xlsx
+++ b/Outputs/PtX_demand_MT.xlsx
@@ -499,10 +499,14 @@
         <v>0.0003362737310847895</v>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.0003931020036790653</v>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>7.83282584682332e-05</v>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
@@ -710,7 +714,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -729,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -779,14 +783,14 @@
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>0.003766560275044659</v>
+        <v>0.004159662278723724</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>0.01137757318133012</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001287322353062497</v>
+        <v>0.001365650611530731</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
@@ -807,10 +811,14 @@
         <v>0.0004347633703284716</v>
       </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.001123514594739524</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0002610293149950294</v>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
     </row>
@@ -1022,7 +1030,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1041,7 +1049,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1091,14 +1099,14 @@
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>0.001253615717623081</v>
+        <v>0.002377130312362605</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>0.0110350275133354</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0006156175813831751</v>
+        <v>0.0008766468963782045</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
@@ -1119,10 +1127,14 @@
         <v>0.000486317278643494</v>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.001316439459079414</v>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.0003813448691330999</v>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
@@ -1342,7 +1354,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1361,7 +1373,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1411,14 +1423,14 @@
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>0.0002317201444341614</v>
+        <v>0.001548159603513576</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>0.01055775858792832</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0001307148919997771</v>
+        <v>0.000512059761132877</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
